--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC109/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBCFA3DE-109A-004C-B601-884BD2170059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717B0264-AEFA-B244-A843-B8628997F0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="52">
   <si>
     <t>Date</t>
   </si>
@@ -101,9 +101,6 @@
   </si>
   <si>
     <t>Storytelling with Visualization</t>
-  </si>
-  <si>
-    <t>mp</t>
   </si>
   <si>
     <t>proj</t>
@@ -201,6 +198,9 @@
   </si>
   <si>
     <t>Text as Data</t>
+  </si>
+  <si>
+    <t>fp01, mp</t>
   </si>
 </sst>
 </file>
@@ -451,10 +451,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -721,7 +721,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="51"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="34" t="s">
         <v>12</v>
       </c>
@@ -754,7 +754,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="51"/>
+      <c r="C5" s="50"/>
       <c r="D5" s="34" t="s">
         <v>12</v>
       </c>
@@ -762,7 +762,7 @@
         <v>45911</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>15</v>
@@ -782,14 +782,14 @@
         <v>45916</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="33"/>
     </row>
     <row r="7" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
-      <c r="C7" s="51"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="34" t="s">
         <v>12</v>
       </c>
@@ -797,7 +797,7 @@
         <v>45918</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>16</v>
@@ -819,7 +819,7 @@
         <v>45923</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="37"/>
@@ -827,7 +827,7 @@
     <row r="9" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="51"/>
+      <c r="C9" s="50"/>
       <c r="D9" s="34" t="s">
         <v>12</v>
       </c>
@@ -861,7 +861,7 @@
         <v>45930</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G10" s="40"/>
       <c r="H10" s="41"/>
@@ -869,7 +869,7 @@
     <row r="11" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="51"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="34" t="s">
         <v>12</v>
       </c>
@@ -877,7 +877,7 @@
         <v>45932</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>18</v>
@@ -889,7 +889,7 @@
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="49">
         <v>6</v>
@@ -901,19 +901,19 @@
         <v>45937</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H12" s="37"/>
     </row>
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="51"/>
+        <v>23</v>
+      </c>
+      <c r="C13" s="50"/>
       <c r="D13" s="30" t="s">
         <v>12</v>
       </c>
@@ -921,7 +921,7 @@
         <v>45939</v>
       </c>
       <c r="F13" s="47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" s="38" t="s">
         <v>18</v>
@@ -944,7 +944,7 @@
         <v>45944</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G14" s="40"/>
       <c r="H14" s="41"/>
@@ -952,9 +952,9 @@
     <row r="15" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="51"/>
+        <v>23</v>
+      </c>
+      <c r="C15" s="50"/>
       <c r="D15" s="30" t="s">
         <v>12</v>
       </c>
@@ -962,7 +962,7 @@
         <v>45946</v>
       </c>
       <c r="F15" s="47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H15" s="36"/>
     </row>
@@ -979,7 +979,7 @@
         <v>45951</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="37"/>
@@ -987,7 +987,7 @@
     <row r="17" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="19"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="51"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="34" t="s">
         <v>12</v>
       </c>
@@ -995,14 +995,14 @@
         <v>45953</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="36"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="20"/>
       <c r="B18" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="49">
         <v>9</v>
@@ -1014,7 +1014,7 @@
         <v>45958</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="37"/>
@@ -1022,9 +1022,9 @@
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21"/>
       <c r="B19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="50"/>
+        <v>23</v>
+      </c>
+      <c r="C19" s="51"/>
       <c r="D19" s="27" t="s">
         <v>12</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>45960</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19" s="22" t="s">
         <v>21</v>
@@ -1053,7 +1053,7 @@
         <v>45965</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20" s="18"/>
       <c r="H20" s="37"/>
@@ -1066,7 +1066,7 @@
       <c r="B21" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="50"/>
+      <c r="C21" s="51"/>
       <c r="D21" s="42" t="s">
         <v>12</v>
       </c>
@@ -1074,12 +1074,10 @@
         <v>45967</v>
       </c>
       <c r="F21" s="45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G21" s="45"/>
-      <c r="H21" s="46" t="s">
-        <v>23</v>
-      </c>
+      <c r="H21" s="46"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="16"/>
@@ -1094,7 +1092,7 @@
         <v>45972</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="37"/>
@@ -1106,7 +1104,7 @@
       <c r="B23" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="50"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="42" t="s">
         <v>12</v>
       </c>
@@ -1114,19 +1112,19 @@
         <v>45974</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G23" s="45" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="46" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="20"/>
       <c r="B24" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="49">
         <v>12</v>
@@ -1138,7 +1136,7 @@
         <v>45979</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="17"/>
       <c r="H24" s="37"/>
@@ -1146,9 +1144,9 @@
     <row r="25" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A25" s="21"/>
       <c r="B25" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="50"/>
+        <v>23</v>
+      </c>
+      <c r="C25" s="51"/>
       <c r="D25" s="27" t="s">
         <v>12</v>
       </c>
@@ -1156,7 +1154,7 @@
         <v>45981</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" s="22" t="s">
         <v>19</v>
@@ -1168,7 +1166,7 @@
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="20"/>
       <c r="B26" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" s="49">
         <v>13</v>
@@ -1180,10 +1178,10 @@
         <v>45986</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H26" s="37" t="s">
         <v>19</v>
@@ -1196,7 +1194,7 @@
       <c r="B27" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="50"/>
+      <c r="C27" s="51"/>
       <c r="D27" s="42" t="s">
         <v>12</v>
       </c>
@@ -1204,7 +1202,7 @@
         <v>45988</v>
       </c>
       <c r="F27" s="44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G27" s="45"/>
       <c r="H27" s="46"/>
@@ -1222,7 +1220,7 @@
         <v>45993</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G28" s="18"/>
       <c r="H28" s="33"/>
@@ -1230,9 +1228,9 @@
     <row r="29" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="24"/>
       <c r="B29" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="50"/>
+        <v>23</v>
+      </c>
+      <c r="C29" s="51"/>
       <c r="D29" s="27" t="s">
         <v>12</v>
       </c>
@@ -1240,7 +1238,7 @@
         <v>45995</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G29" s="22"/>
       <c r="H29" s="39"/>
@@ -1248,7 +1246,7 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" s="16"/>
       <c r="B30" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C30" s="49">
         <v>15</v>
@@ -1260,7 +1258,7 @@
         <v>46000</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G30" s="17"/>
       <c r="H30" s="37"/>
@@ -1270,9 +1268,9 @@
         <v>9</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="50"/>
+        <v>23</v>
+      </c>
+      <c r="C31" s="51"/>
       <c r="D31" s="48" t="s">
         <v>12</v>
       </c>
@@ -1280,11 +1278,11 @@
         <v>46002</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G31" s="23"/>
       <c r="H31" s="39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.15">
@@ -1292,12 +1290,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1307,6 +1299,12 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC109/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abmosca/Documents/Smith/teaching/SDS-CSC109/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717B0264-AEFA-B244-A843-B8628997F0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52C99A43-1440-C24F-BA23-A8935563421A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="620" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sched" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -194,13 +194,16 @@
     <t>NO CLASS - Peer review proposals</t>
   </si>
   <si>
-    <t>FP Workshop - Peer Review</t>
-  </si>
-  <si>
     <t>Text as Data</t>
   </si>
   <si>
     <t>fp01, mp</t>
+  </si>
+  <si>
+    <t>FP Workshop - Peer Review Day 1</t>
+  </si>
+  <si>
+    <t>FP Workshop - Peer Review Day 2</t>
   </si>
 </sst>
 </file>
@@ -451,10 +454,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -721,7 +724,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="50"/>
+      <c r="C3" s="51"/>
       <c r="D3" s="34" t="s">
         <v>12</v>
       </c>
@@ -754,7 +757,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="50"/>
+      <c r="C5" s="51"/>
       <c r="D5" s="34" t="s">
         <v>12</v>
       </c>
@@ -789,7 +792,7 @@
     </row>
     <row r="7" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
-      <c r="C7" s="50"/>
+      <c r="C7" s="51"/>
       <c r="D7" s="34" t="s">
         <v>12</v>
       </c>
@@ -827,7 +830,7 @@
     <row r="9" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="50"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="34" t="s">
         <v>12</v>
       </c>
@@ -869,7 +872,7 @@
     <row r="11" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="50"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="34" t="s">
         <v>12</v>
       </c>
@@ -913,7 +916,7 @@
       <c r="B13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="50"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="30" t="s">
         <v>12</v>
       </c>
@@ -954,7 +957,7 @@
       <c r="B15" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="50"/>
+      <c r="C15" s="51"/>
       <c r="D15" s="30" t="s">
         <v>12</v>
       </c>
@@ -987,7 +990,7 @@
     <row r="17" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="19"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="50"/>
+      <c r="C17" s="51"/>
       <c r="D17" s="34" t="s">
         <v>12</v>
       </c>
@@ -1024,7 +1027,7 @@
       <c r="B19" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="51"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="27" t="s">
         <v>12</v>
       </c>
@@ -1066,7 +1069,7 @@
       <c r="B21" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="51"/>
+      <c r="C21" s="50"/>
       <c r="D21" s="42" t="s">
         <v>12</v>
       </c>
@@ -1104,7 +1107,7 @@
       <c r="B23" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="51"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="42" t="s">
         <v>12</v>
       </c>
@@ -1118,7 +1121,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
@@ -1146,7 +1149,7 @@
       <c r="B25" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="51"/>
+      <c r="C25" s="50"/>
       <c r="D25" s="27" t="s">
         <v>12</v>
       </c>
@@ -1156,12 +1159,8 @@
       <c r="F25" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H25" s="39" t="s">
-        <v>20</v>
-      </c>
+      <c r="G25" s="22"/>
+      <c r="H25" s="39"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="20"/>
@@ -1178,13 +1177,13 @@
         <v>45986</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -1194,7 +1193,7 @@
       <c r="B27" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="51"/>
+      <c r="C27" s="50"/>
       <c r="D27" s="42" t="s">
         <v>12</v>
       </c>
@@ -1220,7 +1219,7 @@
         <v>45993</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G28" s="18"/>
       <c r="H28" s="33"/>
@@ -1230,7 +1229,7 @@
       <c r="B29" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="51"/>
+      <c r="C29" s="50"/>
       <c r="D29" s="27" t="s">
         <v>12</v>
       </c>
@@ -1238,10 +1237,12 @@
         <v>45995</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G29" s="22"/>
-      <c r="H29" s="39"/>
+      <c r="H29" s="39" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" s="16"/>
@@ -1270,7 +1271,7 @@
       <c r="B31" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="51"/>
+      <c r="C31" s="50"/>
       <c r="D31" s="48" t="s">
         <v>12</v>
       </c>
@@ -1290,6 +1291,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1299,12 +1306,6 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abmosca/Documents/Smith/teaching/SDS-CSC109/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B73D75-2C61-AD49-BBA4-2E4B627D0084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C0095E-ECFE-FA42-9CA1-D0E06A14B4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="520" yWindow="600" windowWidth="26360" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="57">
   <si>
     <t>Date</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t xml:space="preserve">a6: Final Vis and Reflection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finals Period -- Final grade consultations </t>
   </si>
 </sst>
 </file>
@@ -453,10 +456,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -727,7 +730,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17"/>
       <c r="B3" s="8"/>
-      <c r="C3" s="53"/>
+      <c r="C3" s="54"/>
       <c r="D3" s="25" t="s">
         <v>13</v>
       </c>
@@ -763,7 +766,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="53"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="25" t="s">
         <v>13</v>
       </c>
@@ -800,7 +803,7 @@
     </row>
     <row r="7" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
-      <c r="C7" s="53"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="25" t="s">
         <v>13</v>
       </c>
@@ -840,7 +843,7 @@
       <c r="B9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="53"/>
+      <c r="C9" s="54"/>
       <c r="D9" s="25" t="s">
         <v>13</v>
       </c>
@@ -878,7 +881,7 @@
       <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="53"/>
+      <c r="C11" s="54"/>
       <c r="D11" s="44" t="s">
         <v>13</v>
       </c>
@@ -920,7 +923,7 @@
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="53"/>
+      <c r="C13" s="54"/>
       <c r="D13" s="25" t="s">
         <v>13</v>
       </c>
@@ -955,7 +958,7 @@
     <row r="15" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="8"/>
-      <c r="C15" s="53"/>
+      <c r="C15" s="54"/>
       <c r="D15" s="25" t="s">
         <v>13</v>
       </c>
@@ -988,7 +991,7 @@
     <row r="17" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="53"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="25" t="s">
         <v>13</v>
       </c>
@@ -1025,7 +1028,7 @@
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="54"/>
+      <c r="C19" s="53"/>
       <c r="D19" s="37" t="s">
         <v>13</v>
       </c>
@@ -1063,7 +1066,7 @@
     <row r="21" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="20"/>
-      <c r="C21" s="54"/>
+      <c r="C21" s="53"/>
       <c r="D21" s="37" t="s">
         <v>13</v>
       </c>
@@ -1099,7 +1102,7 @@
       <c r="B23" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="54"/>
+      <c r="C23" s="53"/>
       <c r="D23" s="37" t="s">
         <v>13</v>
       </c>
@@ -1141,7 +1144,7 @@
       <c r="B25" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="54"/>
+      <c r="C25" s="53"/>
       <c r="D25" s="32" t="s">
         <v>13</v>
       </c>
@@ -1177,7 +1180,7 @@
     <row r="27" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="20"/>
-      <c r="C27" s="54"/>
+      <c r="C27" s="53"/>
       <c r="D27" s="37" t="s">
         <v>13</v>
       </c>
@@ -1213,7 +1216,7 @@
       <c r="B29" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="54"/>
+      <c r="C29" s="53"/>
       <c r="D29" s="37" t="s">
         <v>13</v>
       </c>
@@ -1253,12 +1256,12 @@
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="20"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="41" t="s">
-        <v>13</v>
-      </c>
+      <c r="C31" s="53"/>
+      <c r="D31" s="41"/>
       <c r="E31" s="38"/>
-      <c r="F31" s="20"/>
+      <c r="F31" s="20" t="s">
+        <v>56</v>
+      </c>
       <c r="G31" s="42"/>
       <c r="H31" s="39"/>
     </row>
@@ -1267,6 +1270,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1276,12 +1285,6 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
